--- a/r5-ELGA-MOPED-86-update-test-2/StructureDefinition-moped-ext-konstenmeldungARK.xlsx
+++ b/r5-ELGA-MOPED-86-update-test-2/StructureDefinition-moped-ext-konstenmeldungARK.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T13:02:31+00:00</t>
+    <t>2024-11-06T06:29:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
